--- a/Excel/ROLLER-NEW.xlsx
+++ b/Excel/ROLLER-NEW.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NGODING\BOOS\EXCEL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NGODING\BOOS\BOOS\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5075BFE-30F3-4AFD-9A39-EDB2F5A09185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B40575E-6CE0-4ED0-83D6-00D341903825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{125149BD-17FE-42C2-B7B2-7D98EFA96D65}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="55">
   <si>
     <t>ORDER NUMBER</t>
   </si>
@@ -120,9 +120,6 @@
     <t>Chain</t>
   </si>
   <si>
-    <t>Gear Reduction 38mm</t>
-  </si>
-  <si>
     <t>Black</t>
   </si>
   <si>
@@ -150,9 +147,6 @@
     <t>3RD WIDTH</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Opening Size Face Fit</t>
   </si>
   <si>
@@ -171,10 +165,31 @@
     <t>Cont Plastic Black</t>
   </si>
   <si>
-    <t>No Stopper</t>
-  </si>
-  <si>
-    <t>Oval</t>
+    <t>Your Order Number</t>
+  </si>
+  <si>
+    <t>Your Order Name</t>
+  </si>
+  <si>
+    <t>Your Order Note</t>
+  </si>
+  <si>
+    <t>Room 1</t>
+  </si>
+  <si>
+    <t>With Stopper</t>
+  </si>
+  <si>
+    <t>Flat</t>
+  </si>
+  <si>
+    <t>Fabric on Back</t>
+  </si>
+  <si>
+    <t>Altus</t>
+  </si>
+  <si>
+    <t>No Remote</t>
   </si>
 </sst>
 </file>
@@ -190,12 +205,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -210,8 +231,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -526,12 +548,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D621AC00-7D2F-41C2-8D8F-C89420350C30}">
-  <dimension ref="A1:AG4"/>
+  <dimension ref="A1:AG5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.7109375" customWidth="1"/>
@@ -545,10 +567,10 @@
     <col min="14" max="14" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.42578125" customWidth="1"/>
     <col min="18" max="18" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="11.28515625" customWidth="1"/>
-    <col min="20" max="20" width="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.140625" customWidth="1"/>
     <col min="21" max="21" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
@@ -557,7 +579,7 @@
     <col min="26" max="26" width="26" customWidth="1"/>
     <col min="27" max="27" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.140625" customWidth="1"/>
     <col min="30" max="30" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="14" bestFit="1" customWidth="1"/>
@@ -565,123 +587,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>12312</v>
-      </c>
-      <c r="B2">
-        <v>212</v>
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="R3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG3" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="M3" t="s">
-        <v>11</v>
-      </c>
-      <c r="N3" t="s">
-        <v>12</v>
-      </c>
-      <c r="O3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R3" t="s">
-        <v>39</v>
-      </c>
-      <c r="S3" t="s">
-        <v>40</v>
-      </c>
-      <c r="T3" t="s">
-        <v>38</v>
-      </c>
-      <c r="U3" t="s">
-        <v>17</v>
-      </c>
-      <c r="V3" t="s">
-        <v>18</v>
-      </c>
-      <c r="W3" t="s">
-        <v>19</v>
-      </c>
-      <c r="X3" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -695,49 +720,114 @@
         <v>30</v>
       </c>
       <c r="D4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" t="s">
         <v>31</v>
-      </c>
-      <c r="E4" t="s">
-        <v>32</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
         <v>41</v>
       </c>
-      <c r="H4" t="s">
+      <c r="J4" t="s">
         <v>42</v>
       </c>
-      <c r="I4" t="s">
+      <c r="M4" t="s">
         <v>43</v>
       </c>
-      <c r="J4" t="s">
+      <c r="O4" t="s">
         <v>44</v>
       </c>
-      <c r="M4" t="s">
-        <v>45</v>
-      </c>
-      <c r="O4" t="s">
-        <v>46</v>
-      </c>
       <c r="Q4">
-        <v>2400</v>
+        <v>1000</v>
+      </c>
+      <c r="R4">
+        <v>1000</v>
       </c>
       <c r="T4">
         <v>1000</v>
       </c>
       <c r="U4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="V4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
         <v>49</v>
       </c>
-      <c r="AB4" t="s">
-        <v>32</v>
+      <c r="H5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" t="s">
+        <v>43</v>
+      </c>
+      <c r="O5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q5">
+        <v>1000</v>
+      </c>
+      <c r="R5">
+        <v>1000</v>
+      </c>
+      <c r="T5">
+        <v>1000</v>
+      </c>
+      <c r="U5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
